--- a/submission_documents/audits/formula_table_and_format_audit_20260815.xlsx
+++ b/submission_documents/audits/formula_table_and_format_audit_20260815.xlsx
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6">
@@ -525,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -850,17 +850,17 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Supplement formulas</t>
+          <t>Main formulas</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Equation inventory is exactly (1)–(22b)</t>
+          <t>Outer-fold mean uses the defined fixed fold count F</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>labels=['1', '2', '3', '4', '5a', '5b', '6', '7', '8', '9', '10a', '10b', '11', '12a', '12b', '13', '14', '15', '16', '17a', '17b', '18a', '18b', '19a', '19b', '20a', '20b', '21', '22a', '22b']</t>
+          <t>Gq,e,s(K) = f=1FGq((s,f),K)F,   q ∈ {inv, avail, dep}</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Supplement formulas</t>
+          <t>Main formulas</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Equation (1) contains set-membership operator</t>
+          <t>Endpoint contrast uses the defined primary split-seed count S_main</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>j ∈ C_K</t>
+          <t>Δq(e) = s=1SmainGq,e,s(32) − Gq,e,s(4)Smain</t>
         </is>
       </c>
     </row>
@@ -894,17 +894,17 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Supplement formulas</t>
+          <t>Main formulas</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>No malformed formula glyphs in DOCX math XML</t>
+          <t>Seed-level mean carries an explicit overbar</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>checked all numbered displays</t>
+          <t>Equation 8</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Main tables</t>
+          <t>Main formulas</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Exactly four editable Word tables</t>
+          <t>Operators and descriptive subscripts upright; index q italic</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>count=4</t>
+          <t>upright tokens=['arg max', 'avail', 'dep', 'inv', 'main', 'ref']</t>
         </is>
       </c>
     </row>
@@ -938,17 +938,17 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Main formulas</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Row inventory</t>
+          <t>All display-math runs use explicit Cambria Math 11 pt</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>rows=10; expected=10</t>
+          <t>runs=120; fonts=True; sizes=True</t>
         </is>
       </c>
     </row>
@@ -960,17 +960,17 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Chinese formulas</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Rows cannot split across pages</t>
+          <t>Nine displays are symbol-for-symbol synchronized with the English main text</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>cantSplit=10/10</t>
+          <t>count=9</t>
         </is>
       </c>
     </row>
@@ -982,17 +982,17 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Supplement formulas</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>No vertical borders</t>
+          <t>Equation inventory is exactly (1)–(22b)</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>vertical-border elements=0</t>
+          <t>labels=['1', '2', '3', '4', '5a', '5b', '6', '7', '8', '9', '10a', '10b', '11', '12a', '12b', '13', '14', '15', '16', '17a', '17b', '18a', '18b', '19a', '19b', '20a', '20b', '21', '22a', '22b']</t>
         </is>
       </c>
     </row>
@@ -1004,17 +1004,17 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Supplement formulas</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>No colour or shading</t>
+          <t>Equation (1) contains set-membership operator</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>non-white fills=[]</t>
+          <t>j ∈ C_K</t>
         </is>
       </c>
     </row>
@@ -1026,17 +1026,17 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Supplement formulas</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Header rule is 0.75 pt</t>
+          <t>No malformed formula glyphs in DOCX math XML</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>cells=4/4</t>
+          <t>checked all numbered displays</t>
         </is>
       </c>
     </row>
@@ -1048,17 +1048,17 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Supplement formulas</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Fixed editable table grid</t>
+          <t>Equations (13) and (14) use the same overbar notation as the main text</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>twips=[1757, 1134, 4252, 2098]</t>
+          <t>overbars=1 and 2</t>
         </is>
       </c>
     </row>
@@ -1070,17 +1070,17 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Supplement formulas</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Row inventory</t>
+          <t>All numbered display-math runs use explicit Cambria Math 11 pt</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>rows=6; expected=6</t>
+          <t>runs=433; fonts=True; sizes=True</t>
         </is>
       </c>
     </row>
@@ -1092,17 +1092,17 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Supplement formulas</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Rows cannot split across pages</t>
+          <t>Equation bodies are centred and numbers right-aligned without text boxes</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>cantSplit=6/6</t>
+          <t>tabbed=30/30</t>
         </is>
       </c>
     </row>
@@ -1114,17 +1114,17 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Supplement formulas</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>No vertical borders</t>
+          <t>Mixed descriptive and index subscripts follow mathematical typography</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>vertical-border elements=0</t>
+          <t>best upright; u italic in Equation (2); same constructor used for X/G/L definitions</t>
         </is>
       </c>
     </row>
@@ -1136,17 +1136,17 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Formula-to-data</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>No colour or shading</t>
+          <t>Delta_inv = Delta_avail + Delta_dep holds for every split-seed row</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>non-white fills=[]</t>
+          <t>rows=90; max absolute error=1.041e-16</t>
         </is>
       </c>
     </row>
@@ -1158,17 +1158,17 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Formula-to-code</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Header rule is 0.75 pt</t>
+          <t>Every displayed equation is mapped to an implementation or archived definition</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>cells=4/4</t>
+          <t>mapping rows=32; non-PASS=[]</t>
         </is>
       </c>
     </row>
@@ -1180,17 +1180,17 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Main tables</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Fixed editable table grid</t>
+          <t>Exactly four editable Word tables</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>twips=[1757, 1757, 3402, 2324]</t>
+          <t>count=4</t>
         </is>
       </c>
     </row>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Table 3</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>rows=12; expected=12</t>
+          <t>rows=10; expected=10</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Table 3</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>cantSplit=12/12</t>
+          <t>cantSplit=10/10</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Table 3</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Table 3</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Table 3</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>cells=2/2</t>
+          <t>cells=4/4</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Table 3</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>twips=[2268, 6973]</t>
+          <t>twips=[1757, 1134, 4252, 2098]</t>
         </is>
       </c>
     </row>
@@ -1334,17 +1334,17 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Table 3</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Eleven core symbols retained</t>
+          <t>Row inventory</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>u = (s, f); CK; V(u, j); A(u, j); ĵu(K); jrefinv(−s); jrefdep(−s, K); Ginv(u, K); Gdep(u, K); Gavail(u, K); Δinv(e)</t>
+          <t>rows=6; expected=6</t>
         </is>
       </c>
     </row>
@@ -1356,17 +1356,17 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Table 3</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Symbol column uses text runs rather than formula boxes</t>
+          <t>Rows cannot split across pages</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>OMML objects=0</t>
+          <t>cantSplit=6/6</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1378,17 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Table 4</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Row inventory</t>
+          <t>No vertical borders</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>rows=10; expected=10</t>
+          <t>vertical-border elements=0</t>
         </is>
       </c>
     </row>
@@ -1400,17 +1400,17 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Table 4</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Rows cannot split across pages</t>
+          <t>No colour or shading</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>cantSplit=10/10</t>
+          <t>non-white fills=[]</t>
         </is>
       </c>
     </row>
@@ -1422,17 +1422,17 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Table 4</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>No vertical borders</t>
+          <t>Header rule is 0.75 pt</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>vertical-border elements=0</t>
+          <t>cells=4/4</t>
         </is>
       </c>
     </row>
@@ -1444,17 +1444,17 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Table 4</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>No colour or shading</t>
+          <t>Fixed editable table grid</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>non-white fills=[]</t>
+          <t>twips=[1757, 1757, 3402, 2324]</t>
         </is>
       </c>
     </row>
@@ -1466,17 +1466,17 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Table 4</t>
+          <t>Table 3</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Header rule is 0.75 pt</t>
+          <t>Row inventory</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>cells=5/5</t>
+          <t>rows=12; expected=12</t>
         </is>
       </c>
     </row>
@@ -1488,17 +1488,17 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Table 4</t>
+          <t>Table 3</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Fixed editable table grid</t>
+          <t>Rows cannot split across pages</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>twips=[1304, 2835, 1361, 1361, 2381]</t>
+          <t>cantSplit=12/12</t>
         </is>
       </c>
     </row>
@@ -1510,17 +1510,17 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Table 4</t>
+          <t>Table 3</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Fixed requested column widths</t>
+          <t>No vertical borders</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>actual=[1304, 2835, 1361, 1361, 2381]; target=[1304, 2835, 1361, 1361, 2381]</t>
+          <t>vertical-border elements=0</t>
         </is>
       </c>
     </row>
@@ -1532,17 +1532,17 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Table 4</t>
+          <t>Table 3</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>All endpoint rows retained</t>
+          <t>No colour or shading</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>BACE; BBBP; ClinTox; HIA; P-gp; ESOL; FreeSolv; Lipophilicity; Caco2</t>
+          <t>non-white fills=[]</t>
         </is>
       </c>
     </row>
@@ -1554,17 +1554,17 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Main formatting</t>
+          <t>Table 3</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>No manual page breaks</t>
+          <t>Header rule is 0.75 pt</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>document.xml</t>
+          <t>cells=2/2</t>
         </is>
       </c>
     </row>
@@ -1576,17 +1576,17 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Main formatting</t>
+          <t>Table 3</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Continuous line numbering configured</t>
+          <t>Fixed editable table grid</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>section properties</t>
+          <t>twips=[2268, 6973]</t>
         </is>
       </c>
     </row>
@@ -1598,17 +1598,17 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Main formatting</t>
+          <t>Table 3</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Clean file has no active track revisions</t>
+          <t>Eleven core symbols retained</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>settings.xml</t>
+          <t>u = (s, f); CK; V(u, j); A(u, j); ĵu(K); jrefinv(−s); jrefdep(−s, K); Ginv(u, K); Gdep(u, K); Gavail(u, K); Δinv(e)</t>
         </is>
       </c>
     </row>
@@ -1620,17 +1620,17 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Supplementary workbook</t>
+          <t>Table 3</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Worksheet inventory</t>
+          <t>Symbol column uses text runs rather than formula boxes</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>sheets=64</t>
+          <t>OMML objects=0</t>
         </is>
       </c>
     </row>
@@ -1642,17 +1642,17 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Supplementary workbook</t>
+          <t>Table 4</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>No formula error tokens</t>
+          <t>Row inventory</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>formulas=337; errors=[]</t>
+          <t>rows=10; expected=10</t>
         </is>
       </c>
     </row>
@@ -1664,17 +1664,17 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Additional file 4</t>
+          <t>Table 4</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Outer SHA-256 matches</t>
+          <t>Rows cannot split across pages</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>10B4385D65337D0919AA5B11344519441CF77DC1C9BB4F56051DADF826501A71</t>
+          <t>cantSplit=10/10</t>
         </is>
       </c>
     </row>
@@ -1686,17 +1686,17 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Additional file 4</t>
+          <t>Table 4</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>ZIP CRC and internal SHA-256 manifest</t>
+          <t>No vertical borders</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>version=paper-release-2026-08-r12.9; verified=884/884; bad=None</t>
+          <t>vertical-border elements=0</t>
         </is>
       </c>
     </row>
@@ -1708,17 +1708,17 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Cross-software</t>
+          <t>Table 4</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>WPS formula/table rendering</t>
+          <t>No colour or shading</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>pages=33; Methods 2.5 page=9; Table 3 page=10; symbols copyable=True</t>
+          <t>non-white fills=[]</t>
         </is>
       </c>
     </row>
@@ -1730,15 +1730,279 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
+          <t>Table 4</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Header rule is 0.75 pt</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>cells=5/5</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Table 4</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Fixed editable table grid</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>twips=[1304, 2835, 1361, 1361, 2381]</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Table 4</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Fixed requested column widths</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>actual=[1304, 2835, 1361, 1361, 2381]; target=[1304, 2835, 1361, 1361, 2381]</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Table 4</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>All endpoint rows retained</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>BACE; BBBP; ClinTox; HIA; P-gp; ESOL; FreeSolv; Lipophilicity; Caco2</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Main formatting</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>No manual page breaks</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>document.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Main formatting</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Continuous line numbering configured</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>section properties</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Main formatting</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Clean file has no active track revisions</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>settings.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Supplementary workbook</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Worksheet inventory</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>sheets=64</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Supplementary workbook</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>No formula error tokens</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>formulas=337; errors=[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Additional file 4</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Outer SHA-256 matches</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>10B4385D65337D0919AA5B11344519441CF77DC1C9BB4F56051DADF826501A71</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Additional file 4</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>ZIP CRC and internal SHA-256 manifest</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>version=paper-release-2026-08-r12.9; verified=884/884; bad=None</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>Cross-software</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>WPS formula/table rendering</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>pages=33; Methods 2.5 page=9; Table 3 page=10; symbols copyable=True</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Cross-software</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
         <is>
           <t>LibreOffice formula/table rendering</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>pages=34; Methods 2.5 page=9; Table 3 page=10; symbols copyable=True</t>
         </is>
